--- a/config/default/forms/app/replace_user.xlsx
+++ b/config/default/forms/app/replace_user.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet sheetId="1" name="survey" state="visible" r:id="rId4"/>
@@ -135,6 +135,14 @@
         </r>
       </text>
     </comment>
+    <comment ref="O1" authorId="0">
+      <text>
+        <r>
+          <t xml:space="preserve">Indicates that input for a telephone field should be rejected if the given number is already associated with an existing contact. Requires `cht=https://communityhealthtoolkit.org` to be set in the `namespaces` column on the settings sheet.
+https://docs.communityhealthtoolkit.org/apps/reference/forms/app/#phone-number-input</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -186,7 +194,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C1" authorId="0">
+    <comment ref="B1" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">The unique version code that identifies the current state of the form. A common convention is to use a format like yyyymmddrr. For example, 2017021501 is the 1st revision from Feb 15th, 2017.
@@ -196,7 +204,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="D1" authorId="0">
+    <comment ref="C1" authorId="0">
       <text>
         <r>
           <t xml:space="preserve">Specify different ways of displaying questions. 
@@ -205,12 +213,19 @@
         </r>
       </text>
     </comment>
+    <comment ref="D1" authorId="0">
+      <text>
+        <r>
+          <t>Specify the custom namespaces used in the form. For example: `cht=https://communityhealthtoolkit.org`.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="328">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="311">
   <si>
     <t>type</t>
   </si>
@@ -254,15 +269,15 @@
     <t>instance::db-doc-ref</t>
   </si>
   <si>
+    <t>instance::cht:unique_tel</t>
+  </si>
+  <si>
     <t>begin_group</t>
   </si>
   <si>
     <t>inputs</t>
   </si>
   <si>
-    <t>NO_LABEL</t>
-  </si>
-  <si>
     <t>false()</t>
   </si>
   <si>
@@ -275,39 +290,21 @@
     <t>source</t>
   </si>
   <si>
-    <t>Source</t>
-  </si>
-  <si>
     <t>user</t>
   </si>
   <si>
     <t>source_id</t>
   </si>
   <si>
-    <t>Source ID</t>
-  </si>
-  <si>
     <t>contact_id</t>
   </si>
   <si>
-    <t>User’s Contact ID</t>
-  </si>
-  <si>
     <t>facility_id</t>
   </si>
   <si>
-    <t>Facility ID</t>
-  </si>
-  <si>
-    <t>Username</t>
-  </si>
-  <si>
     <t>phone</t>
   </si>
   <si>
-    <t>Phone Number</t>
-  </si>
-  <si>
     <t>end_group</t>
   </si>
   <si>
@@ -329,28 +326,13 @@
     <t>role</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
     <t>parent</t>
   </si>
   <si>
-    <t>Parent 1 ID</t>
-  </si>
-  <si>
-    <t>Parent 2 ID</t>
-  </si>
-  <si>
-    <t>Parent 3 ID</t>
-  </si>
-  <si>
     <t>calculate</t>
   </si>
   <si>
     <t>patient_id</t>
-  </si>
-  <si>
-    <t>Assocaite form with original contact</t>
   </si>
   <si>
     <t>../inputs/contact/_id</t>
@@ -471,9 +453,6 @@
     <t>${parent_3_id}</t>
   </si>
   <si>
-    <t>Type</t>
-  </si>
-  <si>
     <t>"person"</t>
   </si>
   <si>
@@ -571,6 +550,9 @@
   </si>
   <si>
     <t>dob_method</t>
+  </si>
+  <si>
+    <t>NO_LABEL</t>
   </si>
   <si>
     <t>columns</t>
@@ -627,12 +609,12 @@
     <t>Sex</t>
   </si>
   <si>
-    <t xml:space="preserve">string </t>
-  </si>
-  <si>
     <t>phone_read_only</t>
   </si>
   <si>
+    <t>Phone Number</t>
+  </si>
+  <si>
     <t>${user_phone} != ''</t>
   </si>
   <si>
@@ -642,15 +624,15 @@
     <t>Inherited from existing user</t>
   </si>
   <si>
-    <t>tel</t>
-  </si>
-  <si>
     <t>new_phone</t>
   </si>
   <si>
     <t>${user_phone} = ''</t>
   </si>
   <si>
+    <t>numbers tel</t>
+  </si>
+  <si>
     <t>Please enter a valid local number, or use the standard international format, which includes a plus sign (+) and country code. For example: +254712345678</t>
   </si>
   <si>
@@ -664,6 +646,9 @@
   </si>
   <si>
     <t>select_one roles</t>
+  </si>
+  <si>
+    <t>Role</t>
   </si>
   <si>
     <t>minimal</t>
@@ -795,37 +780,22 @@
     <t>form_title</t>
   </si>
   <si>
-    <t>form_id</t>
-  </si>
-  <si>
     <t>version</t>
   </si>
   <si>
     <t>style</t>
   </si>
   <si>
-    <t>path</t>
-  </si>
-  <si>
-    <t>instance_name</t>
-  </si>
-  <si>
-    <t>default_language</t>
+    <t>namespaces</t>
   </si>
   <si>
     <t>Replace User</t>
   </si>
   <si>
-    <t>replace_user</t>
-  </si>
-  <si>
     <t>pages</t>
   </si>
   <si>
-    <t>data</t>
-  </si>
-  <si>
-    <t>en</t>
+    <t>cht=https://communityhealthtoolkit.org</t>
   </si>
   <si>
     <t>label::hi</t>
@@ -1167,9 +1137,6 @@
     <t>label</t>
   </si>
   <si>
-    <t>namespaces</t>
-  </si>
-  <si>
     <t>choice_filter</t>
   </si>
   <si>
@@ -1183,9 +1150,6 @@
   </si>
   <si>
     <t>instance::cht:duration</t>
-  </si>
-  <si>
-    <t>instance::cht:unique_tel</t>
   </si>
   <si>
     <t>instance::tag</t>
@@ -1224,24 +1188,29 @@
     </font>
     <font>
       <b/>
+      <charset val="1"/>
       <sz val="10"/>
-      <name val="Liberation Sans"/>
+      <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
+      <charset val="1"/>
       <sz val="11"/>
       <name val="Calibri"/>
     </font>
     <font>
+      <charset val="1"/>
       <sz val="11"/>
       <name val="Arial"/>
     </font>
     <font>
+      <charset val="1"/>
       <sz val="11"/>
       <name val="Cambria"/>
     </font>
@@ -1256,7 +1225,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFEFEFEF"/>
-        <bgColor rgb="FFF3F3F3"/>
+        <bgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
     <fill>
@@ -1286,7 +1255,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD9D2E9"/>
-        <bgColor rgb="FFD9D9D9"/>
+        <bgColor rgb="FFD3D3D3"/>
       </patternFill>
     </fill>
     <fill>
@@ -1297,8 +1266,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="65"/>
-        <bgColor rgb="FFF3F3F3"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFEFEFEF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1322,46 +1291,50 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="33">
+  <dxfs count="34">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -1516,6 +1489,13 @@
         <bottom/>
         <diagonal/>
       </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -1821,9 +1801,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office">
   <a:themeElements>
-    <a:clrScheme name="">
+    <a:clrScheme name="LibreOffice">
       <a:dk1>
         <a:srgbClr val="000000"/>
       </a:dk1>
@@ -1831,46 +1811,46 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="18A303"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="0369A3"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="A33E03"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8E03A3"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="C99C00"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="C9211E"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000EE"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="800080"/>
+        <a:srgbClr val="551A8B"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
-        <a:ea typeface="Arial"/>
-        <a:cs typeface="Arial"/>
+        <a:latin typeface="Arial" pitchFamily="0" charset="1"/>
+        <a:ea typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
+        <a:cs typeface="DejaVu Sans" pitchFamily="0" charset="1"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme>
@@ -1878,56 +1858,36 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill/>
-        <a:solidFill/>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="25400">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
-        <a:ln w="38100">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:prstDash val="solid"/>
+          <a:miter/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -1935,42 +1895,43 @@
           <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
         <a:solidFill>
-          <a:srgbClr val="000000"/>
+          <a:schemeClr val="phClr"/>
         </a:solidFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R98"/>
-  <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.44140625" customHeight="1"/>
+  <dimension ref="A1:O98"/>
+  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.4453125" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="27.109375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="32.109375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="53.88671875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="17.44140625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="37.6640625" style="1" customWidth="1"/>
-    <col min="8" max="8" width="32.6640625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="73.88671875" style="1" customWidth="1"/>
+    <col min="1" max="1" width="27.11" style="1" customWidth="1"/>
+    <col min="2" max="2" width="33.11" style="1" customWidth="1"/>
+    <col min="3" max="3" width="32.11" style="1" customWidth="1"/>
+    <col min="4" max="4" width="14.44" style="1" customWidth="1"/>
+    <col min="5" max="5" width="53.88" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.44" style="1" customWidth="1"/>
+    <col min="7" max="7" width="37.67" style="1" customWidth="1"/>
+    <col min="8" max="8" width="32.67" style="1" customWidth="1"/>
+    <col min="9" max="9" width="73.88" style="1" customWidth="1"/>
     <col min="10" max="10" width="30" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="14.44140625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="29.88671875" style="2" customWidth="1"/>
-    <col min="14" max="14" width="29.88671875" style="1" customWidth="1"/>
-    <col min="15" max="16384" width="14.44140625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="14.44" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14.44" style="2" customWidth="1"/>
+    <col min="13" max="13" width="29.88" style="2" customWidth="1"/>
+    <col min="14" max="14" width="29.88" style="1" customWidth="1"/>
+    <col min="15" max="15" width="22.16" style="2" customWidth="1"/>
+    <col min="16" max="65" width="14.44" style="1" customWidth="1"/>
+    <col min="66" max="66" width="9" style="1" customWidth="1"/>
+    <col min="67" max="16384" width="14.44" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2013,17 +1974,18 @@
       <c r="N1" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O1" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
         <v>16</v>
       </c>
+      <c r="C2" s="1"/>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
         <v>17</v>
@@ -2031,25 +1993,18 @@
       <c r="F2" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="1"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O2" s="2"/>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>21</v>
-      </c>
+      <c r="C3" s="1"/>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -2058,523 +2013,258 @@
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="1"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O3" s="2"/>
+    </row>
+    <row r="4" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
+        <v>22</v>
+      </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="1"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O4" s="2"/>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
+        <v>21</v>
+      </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="1"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O5" s="2"/>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
+        <v>23</v>
+      </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="1"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O6" s="2"/>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
+        <v>24</v>
+      </c>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="1"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O7" s="2"/>
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="1"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O8" s="2"/>
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
+        <v>25</v>
+      </c>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O9" s="2"/>
+    </row>
+    <row r="10" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
+        <v>21</v>
+      </c>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="1"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O10" s="2"/>
+    </row>
+    <row r="11" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
+        <v>27</v>
+      </c>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O11" s="2"/>
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>35</v>
+        <v>29</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
       <c r="F12" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
+        <v>31</v>
+      </c>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O12" s="2"/>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
+        <v>32</v>
+      </c>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O13" s="2"/>
+    </row>
+    <row r="14" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C14" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
       <c r="F14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O14" s="2"/>
+    </row>
+    <row r="15" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C15" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
+        <v>29</v>
+      </c>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O15" s="2"/>
+    </row>
+    <row r="16" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O16" s="2"/>
+    </row>
+    <row r="17" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
+        <v>29</v>
+      </c>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O17" s="2"/>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O18" s="2"/>
+    </row>
+    <row r="19" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
+        <v>29</v>
+      </c>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O19" s="2"/>
+    </row>
+    <row r="20" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O20" s="2"/>
+    </row>
+    <row r="21" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O21" s="2"/>
+    </row>
+    <row r="22" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="O22" s="2"/>
+    </row>
+    <row r="23" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
+        <v>27</v>
+      </c>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O23" s="2"/>
+    </row>
+    <row r="24" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
+        <v>16</v>
+      </c>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
-      <c r="N24" s="1"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O24" s="2"/>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
@@ -2588,38 +2278,33 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="26" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="C26" s="1" t="s">
-        <v>46</v>
-      </c>
+        <v>35</v>
+      </c>
+      <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="1"/>
       <c r="I26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
+        <v>36</v>
+      </c>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
-      <c r="N26" s="1"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O26" s="2"/>
+    </row>
+    <row r="27" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
@@ -2628,20 +2313,18 @@
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+        <v>38</v>
+      </c>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
-      <c r="N27" s="1"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O27" s="2"/>
+    </row>
+    <row r="28" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
@@ -2650,20 +2333,18 @@
       <c r="G28" s="1"/>
       <c r="H28" s="1"/>
       <c r="I28" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
+        <v>40</v>
+      </c>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
-      <c r="N28" s="1"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O28" s="2"/>
+    </row>
+    <row r="29" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
@@ -2672,20 +2353,18 @@
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
       <c r="I29" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
+        <v>42</v>
+      </c>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
-      <c r="N29" s="1"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O29" s="2"/>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
@@ -2694,20 +2373,18 @@
       <c r="G30" s="1"/>
       <c r="H30" s="1"/>
       <c r="I30" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
+        <v>44</v>
+      </c>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
-      <c r="N30" s="1"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O30" s="2"/>
+    </row>
+    <row r="31" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
@@ -2716,20 +2393,18 @@
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
       <c r="I31" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
+        <v>46</v>
+      </c>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
-      <c r="N31" s="1"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O31" s="2"/>
+    </row>
+    <row r="32" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
@@ -2738,20 +2413,18 @@
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
       <c r="I32" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
+        <v>48</v>
+      </c>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
-      <c r="N32" s="1"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O32" s="2"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
@@ -2760,20 +2433,18 @@
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
       <c r="I33" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
+        <v>50</v>
+      </c>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
-      <c r="N33" s="1"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O33" s="2"/>
+    </row>
+    <row r="34" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
@@ -2782,143 +2453,111 @@
       <c r="G34" s="1"/>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
+        <v>52</v>
+      </c>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
-      <c r="N34" s="1"/>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O34" s="2"/>
+    </row>
+    <row r="36" ht="13.8" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C36" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
       <c r="F36" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
+        <v>54</v>
+      </c>
       <c r="L36" s="2"/>
       <c r="M36" s="2"/>
-      <c r="N36" s="1"/>
-    </row>
-    <row r="37" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O36" s="2"/>
+    </row>
+    <row r="37" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
       <c r="F37" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
+        <v>58</v>
+      </c>
       <c r="L37" s="2"/>
       <c r="M37" s="2"/>
-      <c r="N37" s="1"/>
-    </row>
-    <row r="38" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O37" s="2"/>
+    </row>
+    <row r="38" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
+        <v>60</v>
+      </c>
       <c r="L38" s="2"/>
       <c r="M38" s="2"/>
-      <c r="N38" s="1"/>
-    </row>
-    <row r="39" ht="12.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O38" s="2"/>
+    </row>
+    <row r="39" ht="12.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="D39" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E39" s="1"/>
       <c r="F39" s="1"/>
       <c r="G39" s="1" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="H39" s="1" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="I39" s="1"/>
       <c r="J39" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="K39" s="1"/>
+        <v>66</v>
+      </c>
       <c r="L39" s="2"/>
       <c r="M39" s="2"/>
-      <c r="N39" s="1"/>
-    </row>
-    <row r="40" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O39" s="2"/>
+    </row>
+    <row r="40" ht="13.8" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
+        <v>53</v>
+      </c>
       <c r="L40" s="2"/>
       <c r="M40" s="2"/>
-      <c r="N40" s="1"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O40" s="2"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -2932,322 +2571,247 @@
       <c r="K42" s="1"/>
       <c r="L42" s="2"/>
       <c r="M42" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="N42" s="1"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>69</v>
+      </c>
+      <c r="O42" s="2"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C43" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
       <c r="F43" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
       <c r="L43" s="2"/>
       <c r="M43" s="2"/>
-      <c r="N43" s="1"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O43" s="2"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="1" t="s">
-        <v>41</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
       <c r="F44" s="1"/>
       <c r="G44" s="1"/>
       <c r="H44" s="1"/>
       <c r="I44" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
+        <v>70</v>
+      </c>
       <c r="L44" s="2"/>
       <c r="M44" s="2"/>
-      <c r="N44" s="1"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O44" s="2"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C45" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F45" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
       <c r="L45" s="2"/>
       <c r="M45" s="2"/>
-      <c r="N45" s="1"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O45" s="2"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C46" s="1" t="s">
-        <v>42</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
       <c r="F46" s="1"/>
       <c r="G46" s="1"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
+        <v>72</v>
+      </c>
       <c r="L46" s="2"/>
       <c r="M46" s="2"/>
-      <c r="N46" s="1"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O46" s="2"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
+        <v>73</v>
+      </c>
       <c r="L47" s="2"/>
       <c r="M47" s="2"/>
-      <c r="N47" s="1"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O47" s="2"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C48" s="1" t="s">
-        <v>43</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
       <c r="F48" s="1"/>
       <c r="G48" s="1"/>
       <c r="H48" s="1"/>
       <c r="I48" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
+        <v>74</v>
+      </c>
       <c r="L48" s="2"/>
       <c r="M48" s="2"/>
-      <c r="N48" s="1"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O48" s="2"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L49" s="2"/>
       <c r="M49" s="2"/>
-      <c r="N49" s="1"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O49" s="2"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L50" s="2"/>
       <c r="M50" s="2"/>
-      <c r="N50" s="1"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O50" s="2"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
+        <v>33</v>
+      </c>
       <c r="L51" s="2"/>
       <c r="M51" s="2"/>
-      <c r="N51" s="1"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O51" s="2"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C52" s="1" t="s">
-        <v>86</v>
-      </c>
+      <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
       <c r="F52" s="1"/>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
+        <v>75</v>
+      </c>
       <c r="L52" s="2"/>
       <c r="M52" s="2"/>
-      <c r="N52" s="1"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O52" s="2"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>1</v>
       </c>
       <c r="C53" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="D53" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
+        <v>63</v>
+      </c>
       <c r="L53" s="2"/>
       <c r="M53" s="2"/>
-      <c r="N53" s="1"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O53" s="2"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>89</v>
+        <v>77</v>
       </c>
       <c r="C54" s="1" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
       <c r="F54" s="1"/>
       <c r="G54" s="1" t="s">
-        <v>91</v>
+        <v>79</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K54" s="1"/>
+        <v>81</v>
+      </c>
       <c r="L54" s="2"/>
       <c r="M54" s="2"/>
-      <c r="N54" s="1"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O54" s="2"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="C55" s="1"/>
       <c r="D55" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E55" s="1"/>
       <c r="F55" s="1"/>
       <c r="G55" s="1"/>
       <c r="H55" s="1"/>
       <c r="I55" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
+        <v>83</v>
+      </c>
       <c r="L55" s="2"/>
       <c r="M55" s="2"/>
-      <c r="N55" s="1"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O55" s="2"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>96</v>
+        <v>84</v>
       </c>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
@@ -3256,180 +2820,149 @@
       <c r="G56" s="1"/>
       <c r="H56" s="1"/>
       <c r="I56" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
+        <v>85</v>
+      </c>
       <c r="L56" s="2"/>
       <c r="M56" s="2"/>
-      <c r="N56" s="1"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O56" s="2"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C57" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
+        <v>86</v>
+      </c>
       <c r="L57" s="2"/>
       <c r="M57" s="2"/>
-      <c r="N57" s="1"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O57" s="2"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="C58" s="1" t="s">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="D58" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E58" s="1" t="s">
-        <v>102</v>
+        <v>90</v>
       </c>
       <c r="F58" s="1"/>
       <c r="G58" s="1" t="s">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="K58" s="1"/>
+        <v>93</v>
+      </c>
       <c r="L58" s="2"/>
       <c r="M58" s="2"/>
-      <c r="N58" s="1"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O58" s="2"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>106</v>
+        <v>94</v>
       </c>
       <c r="C59" s="1" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
+        <v>96</v>
+      </c>
       <c r="L59" s="2"/>
       <c r="M59" s="2"/>
-      <c r="N59" s="1"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O59" s="2"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="C60" s="1" t="s">
-        <v>111</v>
+        <v>99</v>
       </c>
       <c r="D60" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F60" s="1"/>
       <c r="G60" s="1" t="s">
-        <v>112</v>
+        <v>100</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
+        <v>101</v>
+      </c>
       <c r="L60" s="2"/>
       <c r="M60" s="2"/>
-      <c r="N60" s="1"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O60" s="2"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
-        <v>109</v>
+        <v>97</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>114</v>
+        <v>102</v>
       </c>
       <c r="C61" s="1" t="s">
-        <v>115</v>
+        <v>103</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>108</v>
+        <v>96</v>
       </c>
       <c r="F61" s="1"/>
       <c r="G61" s="1" t="s">
-        <v>116</v>
+        <v>104</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
+        <v>105</v>
+      </c>
       <c r="L61" s="2"/>
       <c r="M61" s="2"/>
-      <c r="N61" s="1"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O61" s="2"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
-        <v>118</v>
+        <v>106</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="C62" s="1" t="s">
-        <v>16</v>
+        <v>108</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
       <c r="F62" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
+        <v>109</v>
+      </c>
       <c r="L62" s="2"/>
       <c r="M62" s="2"/>
-      <c r="N62" s="1"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O62" s="2"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
@@ -3438,20 +2971,18 @@
       <c r="G63" s="1"/>
       <c r="H63" s="1"/>
       <c r="I63" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
+        <v>111</v>
+      </c>
       <c r="L63" s="2"/>
       <c r="M63" s="2"/>
-      <c r="N63" s="1"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O63" s="2"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
@@ -3460,20 +2991,18 @@
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
+        <v>113</v>
+      </c>
       <c r="L64" s="2"/>
       <c r="M64" s="2"/>
-      <c r="N64" s="1"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O64" s="2"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
@@ -3482,20 +3011,18 @@
       <c r="G65" s="1"/>
       <c r="H65" s="1"/>
       <c r="I65" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
+        <v>115</v>
+      </c>
       <c r="L65" s="2"/>
       <c r="M65" s="2"/>
-      <c r="N65" s="1"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O65" s="2"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
@@ -3504,20 +3031,18 @@
       <c r="G66" s="1"/>
       <c r="H66" s="1"/>
       <c r="I66" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
+        <v>117</v>
+      </c>
       <c r="L66" s="2"/>
       <c r="M66" s="2"/>
-      <c r="N66" s="1"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O66" s="2"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
@@ -3526,136 +3051,116 @@
       <c r="G67" s="1"/>
       <c r="H67" s="1"/>
       <c r="I67" s="1" t="s">
-        <v>130</v>
-      </c>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
+        <v>119</v>
+      </c>
       <c r="L67" s="2"/>
       <c r="M67" s="2"/>
-      <c r="N67" s="1"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O67" s="2"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="C68" s="1" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
       <c r="L68" s="2"/>
       <c r="M68" s="2"/>
-      <c r="N68" s="1"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O68" s="2"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
+        <v>86</v>
+      </c>
       <c r="L69" s="2"/>
       <c r="M69" s="2"/>
-      <c r="N69" s="1"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O69" s="2"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="C70" s="1" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="D70" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E70" s="1"/>
       <c r="F70" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
+        <v>109</v>
+      </c>
       <c r="L70" s="2"/>
       <c r="M70" s="2"/>
-      <c r="N70" s="1"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O70" s="2"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>136</v>
+        <v>28</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>137</v>
+        <v>125</v>
       </c>
       <c r="C71" s="1" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F71" s="1"/>
       <c r="G71" s="1"/>
       <c r="H71" s="1"/>
       <c r="I71" s="1" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="J71" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="K71" s="1"/>
       <c r="L71" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="M71" s="2"/>
-      <c r="N71" s="1"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O71" s="2"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>142</v>
+        <v>130</v>
       </c>
       <c r="C72" s="1" t="s">
-        <v>31</v>
+        <v>126</v>
       </c>
       <c r="D72" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="F72" s="1"/>
+        <v>131</v>
+      </c>
+      <c r="F72" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="G72" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H72" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I72" s="1"/>
       <c r="J72" s="1"/>
@@ -3663,49 +3168,50 @@
       <c r="L72" s="2"/>
       <c r="M72" s="2"/>
       <c r="N72" s="1"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O72" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="73" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="C73" s="1" t="s">
-        <v>31</v>
-      </c>
+        <v>25</v>
+      </c>
+      <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
       <c r="G73" s="1"/>
       <c r="H73" s="1"/>
       <c r="I73" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
+        <v>134</v>
+      </c>
       <c r="L73" s="2"/>
       <c r="M73" s="2"/>
-      <c r="N73" s="1"/>
-    </row>
-    <row r="74" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O73" s="2"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>141</v>
+        <v>28</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="C74" s="1" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
-      <c r="F74" s="1"/>
+      <c r="F74" s="1" t="s">
+        <v>132</v>
+      </c>
       <c r="G74" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="H74" s="1" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="I74" s="1"/>
       <c r="J74" s="1"/>
@@ -3713,89 +3219,77 @@
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
       <c r="N74" s="1"/>
-    </row>
-    <row r="75" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O74" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="75" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="C75" s="1" t="s">
-        <v>39</v>
+        <v>138</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
       <c r="F75" s="1" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="G75" s="1"/>
       <c r="H75" s="1"/>
       <c r="I75" s="1" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J75" s="1" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="K75" s="1"/>
       <c r="L75" s="2" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="M75" s="2"/>
-      <c r="N75" s="1"/>
-    </row>
-    <row r="76" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O75" s="2"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>151</v>
+        <v>141</v>
       </c>
       <c r="C76" s="1" t="s">
-        <v>152</v>
-      </c>
-      <c r="D76" s="1"/>
-      <c r="E76" s="1"/>
-      <c r="F76" s="1"/>
-      <c r="G76" s="1"/>
-      <c r="H76" s="1"/>
-      <c r="I76" s="1"/>
-      <c r="J76" s="1"/>
-      <c r="K76" s="1"/>
+        <v>142</v>
+      </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
-      <c r="N76" s="1"/>
-    </row>
-    <row r="77" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O76" s="2"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C77" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
       <c r="F77" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G77" s="1"/>
-      <c r="H77" s="1"/>
-      <c r="I77" s="1"/>
-      <c r="J77" s="1"/>
-      <c r="K77" s="1"/>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
-      <c r="N77" s="1"/>
-    </row>
-    <row r="78" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O77" s="2"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
@@ -3804,20 +3298,18 @@
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1" t="s">
-        <v>154</v>
-      </c>
-      <c r="J78" s="1"/>
-      <c r="K78" s="1"/>
+        <v>144</v>
+      </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
-      <c r="N78" s="1"/>
-    </row>
-    <row r="79" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O78" s="2"/>
+    </row>
+    <row r="79" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
@@ -3826,20 +3318,18 @@
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1" t="s">
-        <v>155</v>
-      </c>
-      <c r="J79" s="1"/>
-      <c r="K79" s="1"/>
+        <v>145</v>
+      </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
-      <c r="N79" s="1"/>
-    </row>
-    <row r="80" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O79" s="2"/>
+    </row>
+    <row r="80" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
@@ -3848,40 +3338,29 @@
       <c r="G80" s="1"/>
       <c r="H80" s="1"/>
       <c r="I80" s="1" t="s">
-        <v>156</v>
-      </c>
-      <c r="J80" s="1"/>
-      <c r="K80" s="1"/>
+        <v>146</v>
+      </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
-      <c r="N80" s="1"/>
-    </row>
-    <row r="81" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O80" s="2"/>
+    </row>
+    <row r="81" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B81" s="1" t="s">
-        <v>153</v>
-      </c>
-      <c r="C81" s="1"/>
-      <c r="D81" s="1"/>
-      <c r="E81" s="1"/>
-      <c r="F81" s="1"/>
-      <c r="G81" s="1"/>
-      <c r="H81" s="1"/>
-      <c r="I81" s="1"/>
-      <c r="J81" s="1"/>
-      <c r="K81" s="1"/>
+        <v>143</v>
+      </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
-      <c r="N81" s="1"/>
-    </row>
-    <row r="82" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O81" s="2"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B82" s="1" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
@@ -3890,42 +3369,34 @@
       <c r="G82" s="1"/>
       <c r="H82" s="1"/>
       <c r="I82" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
       <c r="N82" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>149</v>
+      </c>
+      <c r="O82" s="2"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B83" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C83" s="1"/>
-      <c r="D83" s="1"/>
-      <c r="E83" s="1"/>
-      <c r="F83" s="1"/>
-      <c r="G83" s="1"/>
-      <c r="H83" s="1"/>
-      <c r="I83" s="1"/>
-      <c r="J83" s="1"/>
-      <c r="K83" s="1"/>
+        <v>67</v>
+      </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
-      <c r="N83" s="1"/>
-    </row>
-    <row r="84" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O83" s="2"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B84" s="1" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
@@ -3934,22 +3405,23 @@
       <c r="G84" s="1"/>
       <c r="H84" s="1"/>
       <c r="I84" s="1" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
       <c r="N84" s="1" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="85" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+      <c r="O84" s="2"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B85" s="1" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
@@ -3958,20 +3430,18 @@
       <c r="G85" s="1"/>
       <c r="H85" s="1"/>
       <c r="I85" s="1" t="s">
-        <v>163</v>
-      </c>
-      <c r="J85" s="1"/>
-      <c r="K85" s="1"/>
+        <v>153</v>
+      </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
-      <c r="N85" s="1"/>
-    </row>
-    <row r="86" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O85" s="2"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="B86" s="1" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
@@ -3980,193 +3450,85 @@
       <c r="G86" s="1"/>
       <c r="H86" s="1"/>
       <c r="I86" s="1" t="s">
-        <v>165</v>
-      </c>
-      <c r="J86" s="1"/>
-      <c r="K86" s="1"/>
+        <v>155</v>
+      </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
-      <c r="N86" s="1"/>
-    </row>
-    <row r="87" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
-      <c r="C87" s="1"/>
-      <c r="D87" s="1"/>
-      <c r="E87" s="1"/>
-      <c r="F87" s="1"/>
-      <c r="G87" s="1"/>
-      <c r="H87" s="1"/>
-      <c r="I87" s="1"/>
-      <c r="J87" s="1"/>
-    </row>
-    <row r="88" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O86" s="2"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="88" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B88" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C88" s="1" t="s">
-        <v>16</v>
-      </c>
+        <v>156</v>
+      </c>
+      <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
       <c r="F88" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="G88" s="1"/>
-      <c r="H88" s="1"/>
-      <c r="I88" s="1"/>
-      <c r="J88" s="1"/>
-      <c r="K88" s="1"/>
+        <v>54</v>
+      </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
-      <c r="N88" s="1"/>
-    </row>
-    <row r="89" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O88" s="2"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B89" s="1" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
       <c r="F89" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="G89" s="1"/>
-      <c r="H89" s="1"/>
-      <c r="I89" s="1"/>
-      <c r="J89" s="1"/>
-      <c r="K89" s="1"/>
+        <v>58</v>
+      </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
-      <c r="N89" s="1"/>
-    </row>
-    <row r="90" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O89" s="2"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B90" s="1" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="C90" s="1" t="s">
-        <v>167</v>
-      </c>
-      <c r="D90" s="1"/>
-      <c r="E90" s="1"/>
-      <c r="F90" s="1"/>
-      <c r="G90" s="1"/>
-      <c r="H90" s="1"/>
-      <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="1"/>
+        <v>157</v>
+      </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
-      <c r="N90" s="1"/>
-    </row>
-    <row r="91" ht="15.75" customHeight="1" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="O90" s="2"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>166</v>
-      </c>
-      <c r="C91" s="1"/>
-      <c r="D91" s="1"/>
-      <c r="E91" s="1"/>
-      <c r="F91" s="1"/>
-      <c r="G91" s="1"/>
-      <c r="H91" s="1"/>
-      <c r="I91" s="1"/>
-      <c r="J91" s="1"/>
-      <c r="K91" s="1"/>
+        <v>156</v>
+      </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
-      <c r="N91" s="1"/>
-    </row>
-    <row r="92" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
-      <c r="C92" s="1"/>
-      <c r="D92" s="1"/>
-      <c r="E92" s="1"/>
-      <c r="F92" s="1"/>
-      <c r="G92" s="1"/>
-      <c r="H92" s="1"/>
-      <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-    </row>
-    <row r="93" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
-      <c r="C93" s="1"/>
-      <c r="D93" s="1"/>
-      <c r="E93" s="1"/>
-      <c r="F93" s="1"/>
-      <c r="G93" s="1"/>
-      <c r="H93" s="1"/>
-      <c r="I93" s="1"/>
-      <c r="J93" s="1"/>
-    </row>
-    <row r="94" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
-      <c r="C94" s="1"/>
-      <c r="D94" s="1"/>
-      <c r="E94" s="1"/>
-      <c r="F94" s="1"/>
-      <c r="G94" s="1"/>
-      <c r="H94" s="1"/>
-      <c r="I94" s="1"/>
-      <c r="J94" s="1"/>
-    </row>
-    <row r="95" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
-      <c r="C95" s="1"/>
-      <c r="D95" s="1"/>
-      <c r="E95" s="1"/>
-      <c r="F95" s="1"/>
-      <c r="G95" s="1"/>
-      <c r="H95" s="1"/>
-      <c r="I95" s="1"/>
-      <c r="J95" s="1"/>
-    </row>
-    <row r="96" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
-      <c r="C96" s="1"/>
-      <c r="D96" s="1"/>
-      <c r="E96" s="1"/>
-      <c r="F96" s="1"/>
-      <c r="G96" s="1"/>
-      <c r="H96" s="1"/>
-      <c r="I96" s="1"/>
-      <c r="J96" s="1"/>
-    </row>
-    <row r="97" ht="15.75" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
-      <c r="C97" s="1"/>
-      <c r="D97" s="1"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
-      <c r="G97" s="1"/>
-      <c r="H97" s="1"/>
-      <c r="I97" s="1"/>
-      <c r="J97" s="1"/>
-    </row>
+      <c r="O91" s="2"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <conditionalFormatting sqref="A1:BM1">
+  <conditionalFormatting sqref="A1:BN1">
     <cfRule type="expression" dxfId="0" priority="1">
-      <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BM$1,A1)&gt;1)</formula>
+      <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BN$1,A1)&gt;1)</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
       <formula>AND(A1&lt;&gt;"",NOT(OR(A1="audio",LEFT(A1,7)="audio::",A1="constraint_message",LEFT(A1,20)="constraint_message::",A1="hint",LEFT(A1,6)="hint::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="required_message",LEFT(A1,18)="required_message::",A1="video",LEFT(A1,7)="video::")),NOT(NOT(ISERROR(MATCH(A1,{"appearance","instance::cht:duration","instance::cht:unique_tel","instance::db-doc","instance::db-doc-ref","instance::tag","instance::type","name","note","parameters","read_only","trigger","type"},0)))),NOT(NOT(ISERROR(MATCH(A1,{"calculation","choice_filter","constraint","default","relevant","repeat_count","required"},0)))))</formula>
@@ -4195,64 +3557,69 @@
       <formula>AND(A2&lt;&gt;"",NOT(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","begin_group","begin_repeat","calculate","date","datetime","decimal","end","end_group","end_repeat","file","geopoint","geoshape","geotrace","hidden","image","integer","note","range","rank","start","text","time","today","video"},0))),AND(LEFT(A2,11)="select_one ",NOT(ISERROR(MATCH(MID(A2,12,999),choices!$A:$A,0)))),AND(LEFT(A2,16)="select_multiple ",NOT(ISERROR(MATCH(MID(A2,17,999),choices!$A:$A,0)))))))</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="O2:O1098">
+    <cfRule type="expression" dxfId="9" priority="1">
+      <formula>AND(O2&lt;&gt;"",O2&lt;&gt;"true")</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="M2:M1098">
-    <cfRule type="expression" dxfId="9" priority="1">
+    <cfRule type="expression" dxfId="10" priority="1">
       <formula>AND(M2&lt;&gt;"",M2&lt;&gt;"true")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="L2:L1098">
-    <cfRule type="expression" dxfId="10" priority="1">
+    <cfRule type="expression" dxfId="11" priority="1">
       <formula>AND(L2&lt;&gt;"",L2&lt;&gt;"true")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B2:B1098">
-    <cfRule type="expression" dxfId="11" priority="1">
+    <cfRule type="expression" dxfId="12" priority="1">
       <formula>AND(A2&lt;&gt;"",B2="")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="C2:C1098">
-    <cfRule type="expression" dxfId="12" priority="1">
+    <cfRule type="expression" dxfId="13" priority="1">
       <formula>AND(OR(NOT(ISERROR(MATCH(A2,{"acknowledge","audio","date","datetime","decimal","file","geopoint","geoshape","geotrace","image","integer","note","range","rank","text","time","video"},0))),LEFT(A2,11)="select_one ",LEFT(A2,16)="select_multiple "),C2="")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="13" priority="2">
+    <cfRule type="expression" dxfId="14" priority="2">
       <formula>AND(C2&lt;&gt;"",NOT(ISERROR(MATCH(A2,{"calculate","end","end_group","end_repeat","hidden","start","today"},0))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="14" priority="3">
+    <cfRule type="expression" dxfId="15" priority="3">
       <formula>OR(C2="NO_LABEL",C2="DELETE_THIS_LINE")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I2:I1098">
-    <cfRule type="expression" dxfId="15" priority="1">
+    <cfRule type="expression" dxfId="16" priority="1">
       <formula>AND(A2="calculate",I2="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BM1098">
-    <cfRule type="expression" dxfId="16" priority="1">
+  <conditionalFormatting sqref="A2:BN1098">
+    <cfRule type="expression" dxfId="17" priority="1">
       <formula>AND($A2="begin_group",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BM1098">
-    <cfRule type="expression" dxfId="17" priority="1">
+  <conditionalFormatting sqref="A2:BN1098">
+    <cfRule type="expression" dxfId="18" priority="1">
       <formula>AND($A2="end_group",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BM1098">
-    <cfRule type="expression" dxfId="18" priority="1">
+  <conditionalFormatting sqref="A2:BN1098">
+    <cfRule type="expression" dxfId="19" priority="1">
       <formula>AND($A2="begin_repeat",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BM1098">
-    <cfRule type="expression" dxfId="19" priority="1">
+  <conditionalFormatting sqref="A2:BN1098">
+    <cfRule type="expression" dxfId="20" priority="1">
       <formula>AND($A2="end_repeat",A$1&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BM1098">
-    <cfRule type="expression" dxfId="20" priority="1">
+  <conditionalFormatting sqref="A2:BN1098">
+    <cfRule type="expression" dxfId="21" priority="1">
       <formula>AND(A2&lt;&gt;"",A$1="")</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Column warning" error="For translatable columns, you can append &quot;::&lt;lang&gt;&quot; to the column name (e.g., label::en)." sqref="A1:BM1">
+  <dataValidations count="5">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Column warning" error="For translatable columns, you can append &quot;::&lt;lang&gt;&quot; to the column name (e.g., label::en)." sqref="A1:BN1">
       <formula1>'chtx'!$A$2:$A$28</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Type warning" error="If configuring a select, ensure your list name matches a list from the choices sheet." sqref="A2:A1098">
@@ -4264,27 +3631,30 @@
     <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="This column only accepts &quot;true&quot; or an empty value." sqref="M2:M1098">
       <formula1>",true"</formula1>
     </dataValidation>
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="This column only accepts &quot;true&quot; or an empty value." sqref="O2:O1098">
+      <formula1>",true"</formula1>
+    </dataValidation>
   </dataValidations>
-  <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.752083333333333" bottom="0.752083333333333" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" copies="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:R73"/>
-  <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.44140625" customHeight="1"/>
+  <dimension ref="A1:C73"/>
+  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.4453125" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="25.88671875" style="1" customWidth="1"/>
-    <col min="3" max="15" width="45.88671875" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="14.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="28.33" style="1" customWidth="1"/>
+    <col min="2" max="2" width="25.88" style="1" customWidth="1"/>
+    <col min="3" max="15" width="45.88" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="14.44" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
@@ -4292,1536 +3662,189 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
-      <c r="H1" s="1"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="3" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>163</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="5" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>169</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="C7" s="1" t="s">
         <v>170</v>
       </c>
-      <c r="C2" s="1" t="s">
+    </row>
+    <row r="8" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
-      <c r="O2" s="1"/>
-      <c r="P2" s="1"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-    </row>
-    <row r="3" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-      <c r="G3" s="1"/>
-      <c r="H3" s="1"/>
-      <c r="I3" s="1"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-      <c r="Q3" s="1"/>
-      <c r="R3" s="1"/>
-    </row>
-    <row r="4" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="C8" s="1" t="s">
         <v>172</v>
       </c>
-      <c r="B4" s="1" t="s">
+    </row>
+    <row r="9" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>173</v>
       </c>
-      <c r="C4" s="1" t="s">
+      <c r="C9" s="1" t="s">
         <v>174</v>
       </c>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-      <c r="Q4" s="1"/>
-      <c r="R4" s="1"/>
-    </row>
-    <row r="5" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B5" s="1" t="s">
+    </row>
+    <row r="10" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
         <v>175</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
-      <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
-      <c r="R5" s="1"/>
-    </row>
-    <row r="6" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B6" s="1" t="s">
+      <c r="C11" s="1" t="s">
         <v>177</v>
       </c>
-      <c r="C6" s="1" t="s">
+    </row>
+    <row r="12" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="1"/>
-    </row>
-    <row r="7" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B7" s="1" t="s">
+      <c r="C12" s="1" t="s">
         <v>179</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>180</v>
-      </c>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
-      <c r="N7" s="1"/>
-      <c r="O7" s="1"/>
-      <c r="P7" s="1"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="1"/>
-    </row>
-    <row r="8" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" s="1" t="s">
-        <v>181</v>
-      </c>
-      <c r="C8" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
-      <c r="N8" s="1"/>
-      <c r="O8" s="1"/>
-      <c r="P8" s="1"/>
-      <c r="Q8" s="1"/>
-      <c r="R8" s="1"/>
-    </row>
-    <row r="9" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="B9" s="1" t="s">
-        <v>183</v>
-      </c>
-      <c r="C9" s="1" t="s">
-        <v>184</v>
-      </c>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
-      <c r="N9" s="1"/>
-      <c r="O9" s="1"/>
-      <c r="P9" s="1"/>
-      <c r="Q9" s="1"/>
-      <c r="R9" s="1"/>
-    </row>
-    <row r="10" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
-      <c r="C10" s="1"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
-      <c r="N10" s="1"/>
-      <c r="O10" s="1"/>
-      <c r="P10" s="1"/>
-      <c r="Q10" s="1"/>
-      <c r="R10" s="1"/>
-    </row>
-    <row r="11" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B11" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>187</v>
-      </c>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
-      <c r="N11" s="1"/>
-      <c r="O11" s="1"/>
-      <c r="P11" s="1"/>
-      <c r="Q11" s="1"/>
-      <c r="R11" s="1"/>
-    </row>
-    <row r="12" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>185</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>189</v>
-      </c>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
-      <c r="N12" s="1"/>
-      <c r="O12" s="1"/>
-      <c r="P12" s="1"/>
-      <c r="Q12" s="1"/>
-      <c r="R12" s="1"/>
-    </row>
-    <row r="13" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
-      <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="1"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
-      <c r="N13" s="1"/>
-      <c r="O13" s="1"/>
-      <c r="P13" s="1"/>
-      <c r="Q13" s="1"/>
-      <c r="R13" s="1"/>
-    </row>
-    <row r="14" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
-      <c r="C14" s="1"/>
-      <c r="D14" s="1"/>
-      <c r="E14" s="1"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
-      <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="1"/>
-    </row>
-    <row r="15" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
-      <c r="C15" s="1"/>
-      <c r="D15" s="1"/>
-      <c r="E15" s="1"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-      <c r="N15" s="1"/>
-      <c r="O15" s="1"/>
-      <c r="P15" s="1"/>
-      <c r="Q15" s="1"/>
-      <c r="R15" s="1"/>
-    </row>
-    <row r="16" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
-      <c r="C16" s="1"/>
-      <c r="D16" s="1"/>
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="1"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1"/>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1"/>
-    </row>
-    <row r="17" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
-      <c r="C17" s="1"/>
-      <c r="D17" s="1"/>
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="1"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="1"/>
-      <c r="L17" s="1"/>
-      <c r="M17" s="1"/>
-      <c r="N17" s="1"/>
-      <c r="O17" s="1"/>
-      <c r="P17" s="1"/>
-      <c r="Q17" s="1"/>
-      <c r="R17" s="1"/>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
-      <c r="D18" s="1"/>
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="1"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="1"/>
-      <c r="M18" s="1"/>
-      <c r="N18" s="1"/>
-      <c r="O18" s="1"/>
-      <c r="P18" s="1"/>
-      <c r="Q18" s="1"/>
-      <c r="R18" s="1"/>
-    </row>
-    <row r="19" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
-      <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="1"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
-      <c r="M19" s="1"/>
-      <c r="N19" s="1"/>
-      <c r="O19" s="1"/>
-      <c r="P19" s="1"/>
-      <c r="Q19" s="1"/>
-      <c r="R19" s="1"/>
-    </row>
-    <row r="20" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
-      <c r="C20" s="1"/>
-      <c r="D20" s="1"/>
-      <c r="E20" s="1"/>
-      <c r="F20" s="1"/>
-      <c r="G20" s="1"/>
-      <c r="H20" s="1"/>
-      <c r="I20" s="1"/>
-      <c r="J20" s="1"/>
-      <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
-      <c r="M20" s="1"/>
-      <c r="N20" s="1"/>
-      <c r="O20" s="1"/>
-      <c r="P20" s="1"/>
-      <c r="Q20" s="1"/>
-      <c r="R20" s="1"/>
-    </row>
-    <row r="21" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
-      <c r="C21" s="1"/>
-      <c r="D21" s="1"/>
-      <c r="E21" s="1"/>
-      <c r="F21" s="1"/>
-      <c r="G21" s="1"/>
-      <c r="H21" s="1"/>
-      <c r="I21" s="1"/>
-      <c r="J21" s="1"/>
-      <c r="K21" s="1"/>
-      <c r="L21" s="1"/>
-      <c r="M21" s="1"/>
-      <c r="N21" s="1"/>
-      <c r="O21" s="1"/>
-      <c r="P21" s="1"/>
-      <c r="Q21" s="1"/>
-      <c r="R21" s="1"/>
-    </row>
-    <row r="22" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
-      <c r="C22" s="1"/>
-      <c r="D22" s="1"/>
-      <c r="E22" s="1"/>
-      <c r="F22" s="1"/>
-      <c r="G22" s="1"/>
-      <c r="H22" s="1"/>
-      <c r="I22" s="1"/>
-      <c r="J22" s="1"/>
-      <c r="K22" s="1"/>
-      <c r="L22" s="1"/>
-      <c r="M22" s="1"/>
-      <c r="N22" s="1"/>
-      <c r="O22" s="1"/>
-      <c r="P22" s="1"/>
-      <c r="Q22" s="1"/>
-      <c r="R22" s="1"/>
-    </row>
-    <row r="23" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
-      <c r="C23" s="1"/>
-      <c r="D23" s="1"/>
-      <c r="E23" s="1"/>
-      <c r="F23" s="1"/>
-      <c r="G23" s="1"/>
-      <c r="H23" s="1"/>
-      <c r="I23" s="1"/>
-      <c r="J23" s="1"/>
-      <c r="K23" s="1"/>
-      <c r="L23" s="1"/>
-      <c r="M23" s="1"/>
-      <c r="N23" s="1"/>
-      <c r="O23" s="1"/>
-      <c r="P23" s="1"/>
-      <c r="Q23" s="1"/>
-      <c r="R23" s="1"/>
-    </row>
-    <row r="24" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
-      <c r="C24" s="1"/>
-      <c r="D24" s="1"/>
-      <c r="E24" s="1"/>
-      <c r="F24" s="1"/>
-      <c r="G24" s="1"/>
-      <c r="H24" s="1"/>
-      <c r="I24" s="1"/>
-      <c r="J24" s="1"/>
-      <c r="K24" s="1"/>
-      <c r="L24" s="1"/>
-      <c r="M24" s="1"/>
-      <c r="N24" s="1"/>
-      <c r="O24" s="1"/>
-      <c r="P24" s="1"/>
-      <c r="Q24" s="1"/>
-      <c r="R24" s="1"/>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
-      <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
-      <c r="E25" s="1"/>
-      <c r="F25" s="1"/>
-      <c r="G25" s="1"/>
-      <c r="H25" s="1"/>
-      <c r="I25" s="1"/>
-      <c r="J25" s="1"/>
-      <c r="K25" s="1"/>
-      <c r="L25" s="1"/>
-      <c r="M25" s="1"/>
-      <c r="N25" s="1"/>
-      <c r="O25" s="1"/>
-      <c r="P25" s="1"/>
-      <c r="Q25" s="1"/>
-      <c r="R25" s="1"/>
-    </row>
-    <row r="26" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
-      <c r="C26" s="1"/>
-      <c r="D26" s="1"/>
-      <c r="E26" s="1"/>
-      <c r="F26" s="1"/>
-      <c r="G26" s="1"/>
-      <c r="H26" s="1"/>
-      <c r="I26" s="1"/>
-      <c r="J26" s="1"/>
-      <c r="K26" s="1"/>
-      <c r="L26" s="1"/>
-      <c r="M26" s="1"/>
-      <c r="N26" s="1"/>
-      <c r="O26" s="1"/>
-      <c r="P26" s="1"/>
-      <c r="Q26" s="1"/>
-      <c r="R26" s="1"/>
-    </row>
-    <row r="27" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
-      <c r="C27" s="1"/>
-      <c r="D27" s="1"/>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
-      <c r="G27" s="1"/>
-      <c r="H27" s="1"/>
-      <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
-      <c r="L27" s="1"/>
-      <c r="M27" s="1"/>
-      <c r="N27" s="1"/>
-      <c r="O27" s="1"/>
-      <c r="P27" s="1"/>
-      <c r="Q27" s="1"/>
-      <c r="R27" s="1"/>
-    </row>
-    <row r="28" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
-      <c r="C28" s="1"/>
-      <c r="D28" s="1"/>
-      <c r="E28" s="1"/>
-      <c r="F28" s="1"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="1"/>
-      <c r="I28" s="1"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="1"/>
-      <c r="L28" s="1"/>
-      <c r="M28" s="1"/>
-      <c r="N28" s="1"/>
-      <c r="O28" s="1"/>
-      <c r="P28" s="1"/>
-      <c r="Q28" s="1"/>
-      <c r="R28" s="1"/>
-    </row>
-    <row r="29" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
-      <c r="C29" s="1"/>
-      <c r="D29" s="1"/>
-      <c r="E29" s="1"/>
-      <c r="F29" s="1"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
-      <c r="J29" s="1"/>
-      <c r="K29" s="1"/>
-      <c r="L29" s="1"/>
-      <c r="M29" s="1"/>
-      <c r="N29" s="1"/>
-      <c r="O29" s="1"/>
-      <c r="P29" s="1"/>
-      <c r="Q29" s="1"/>
-      <c r="R29" s="1"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
-      <c r="C30" s="1"/>
-      <c r="D30" s="1"/>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="1"/>
-      <c r="I30" s="1"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-    </row>
-    <row r="31" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
-      <c r="C31" s="1"/>
-      <c r="D31" s="1"/>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
-      <c r="H31" s="1"/>
-      <c r="I31" s="1"/>
-      <c r="J31" s="1"/>
-      <c r="K31" s="1"/>
-      <c r="L31" s="1"/>
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-    </row>
-    <row r="32" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
-      <c r="C32" s="1"/>
-      <c r="D32" s="1"/>
-      <c r="E32" s="1"/>
-      <c r="F32" s="1"/>
-      <c r="G32" s="1"/>
-      <c r="H32" s="1"/>
-      <c r="I32" s="1"/>
-      <c r="J32" s="1"/>
-      <c r="K32" s="1"/>
-      <c r="L32" s="1"/>
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-    </row>
-    <row r="33" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
-      <c r="C33" s="1"/>
-      <c r="D33" s="1"/>
-      <c r="E33" s="1"/>
-      <c r="F33" s="1"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="1"/>
-      <c r="I33" s="1"/>
-      <c r="J33" s="1"/>
-      <c r="K33" s="1"/>
-      <c r="L33" s="1"/>
-      <c r="M33" s="1"/>
-      <c r="N33" s="1"/>
-      <c r="O33" s="1"/>
-      <c r="P33" s="1"/>
-      <c r="Q33" s="1"/>
-      <c r="R33" s="1"/>
-    </row>
-    <row r="34" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
-      <c r="C34" s="1"/>
-      <c r="D34" s="1"/>
-      <c r="E34" s="1"/>
-      <c r="F34" s="1"/>
-      <c r="G34" s="1"/>
-      <c r="H34" s="1"/>
-      <c r="I34" s="1"/>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1"/>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
-      <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
-      <c r="R34" s="1"/>
-    </row>
-    <row r="35" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
-      <c r="C35" s="1"/>
-      <c r="D35" s="1"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
-      <c r="G35" s="1"/>
-      <c r="H35" s="1"/>
-      <c r="I35" s="1"/>
-      <c r="J35" s="1"/>
-      <c r="K35" s="1"/>
-      <c r="L35" s="1"/>
-      <c r="M35" s="1"/>
-      <c r="N35" s="1"/>
-      <c r="O35" s="1"/>
-      <c r="P35" s="1"/>
-      <c r="Q35" s="1"/>
-      <c r="R35" s="1"/>
-    </row>
-    <row r="36" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
-      <c r="C36" s="1"/>
-      <c r="D36" s="1"/>
-      <c r="E36" s="1"/>
-      <c r="F36" s="1"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="1"/>
-      <c r="I36" s="1"/>
-      <c r="J36" s="1"/>
-      <c r="K36" s="1"/>
-      <c r="L36" s="1"/>
-      <c r="M36" s="1"/>
-      <c r="N36" s="1"/>
-      <c r="O36" s="1"/>
-      <c r="P36" s="1"/>
-      <c r="Q36" s="1"/>
-      <c r="R36" s="1"/>
-    </row>
-    <row r="37" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
-      <c r="C37" s="1"/>
-      <c r="D37" s="1"/>
-      <c r="E37" s="1"/>
-      <c r="F37" s="1"/>
-      <c r="G37" s="1"/>
-      <c r="H37" s="1"/>
-      <c r="I37" s="1"/>
-      <c r="J37" s="1"/>
-      <c r="K37" s="1"/>
-      <c r="L37" s="1"/>
-      <c r="M37" s="1"/>
-      <c r="N37" s="1"/>
-      <c r="O37" s="1"/>
-      <c r="P37" s="1"/>
-      <c r="Q37" s="1"/>
-      <c r="R37" s="1"/>
-    </row>
-    <row r="38" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
-      <c r="C38" s="1"/>
-      <c r="D38" s="1"/>
-      <c r="E38" s="1"/>
-      <c r="F38" s="1"/>
-      <c r="G38" s="1"/>
-      <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
-      <c r="M38" s="1"/>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
-      <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
-      <c r="R38" s="1"/>
-    </row>
-    <row r="39" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
-      <c r="C39" s="1"/>
-      <c r="D39" s="1"/>
-      <c r="E39" s="1"/>
-      <c r="F39" s="1"/>
-      <c r="G39" s="1"/>
-      <c r="H39" s="1"/>
-      <c r="I39" s="1"/>
-      <c r="J39" s="1"/>
-      <c r="K39" s="1"/>
-      <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
-      <c r="N39" s="1"/>
-      <c r="O39" s="1"/>
-      <c r="P39" s="1"/>
-      <c r="Q39" s="1"/>
-      <c r="R39" s="1"/>
-    </row>
-    <row r="40" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
-      <c r="C40" s="1"/>
-      <c r="D40" s="1"/>
-      <c r="E40" s="1"/>
-      <c r="F40" s="1"/>
-      <c r="G40" s="1"/>
-      <c r="H40" s="1"/>
-      <c r="I40" s="1"/>
-      <c r="J40" s="1"/>
-      <c r="K40" s="1"/>
-      <c r="L40" s="1"/>
-      <c r="M40" s="1"/>
-      <c r="N40" s="1"/>
-      <c r="O40" s="1"/>
-      <c r="P40" s="1"/>
-      <c r="Q40" s="1"/>
-      <c r="R40" s="1"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
-      <c r="C41" s="1"/>
-      <c r="D41" s="1"/>
-      <c r="E41" s="1"/>
-      <c r="F41" s="1"/>
-      <c r="G41" s="1"/>
-      <c r="H41" s="1"/>
-      <c r="I41" s="1"/>
-      <c r="J41" s="1"/>
-      <c r="K41" s="1"/>
-      <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
-      <c r="N41" s="1"/>
-      <c r="O41" s="1"/>
-      <c r="P41" s="1"/>
-      <c r="Q41" s="1"/>
-      <c r="R41" s="1"/>
-    </row>
-    <row r="42" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
-      <c r="C42" s="1"/>
-      <c r="D42" s="1"/>
-      <c r="E42" s="1"/>
-      <c r="F42" s="1"/>
-      <c r="G42" s="1"/>
-      <c r="H42" s="1"/>
-      <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
-      <c r="M42" s="1"/>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
-      <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
-      <c r="R42" s="1"/>
-    </row>
-    <row r="43" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
-      <c r="C43" s="1"/>
-      <c r="D43" s="1"/>
-      <c r="E43" s="1"/>
-      <c r="F43" s="1"/>
-      <c r="G43" s="1"/>
-      <c r="H43" s="1"/>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1"/>
-      <c r="K43" s="1"/>
-      <c r="L43" s="1"/>
-      <c r="M43" s="1"/>
-      <c r="N43" s="1"/>
-      <c r="O43" s="1"/>
-      <c r="P43" s="1"/>
-      <c r="Q43" s="1"/>
-      <c r="R43" s="1"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
-      <c r="C44" s="1"/>
-      <c r="D44" s="1"/>
-      <c r="E44" s="1"/>
-      <c r="F44" s="1"/>
-      <c r="G44" s="1"/>
-      <c r="H44" s="1"/>
-      <c r="I44" s="1"/>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
-      <c r="M44" s="1"/>
-      <c r="N44" s="1"/>
-      <c r="O44" s="1"/>
-      <c r="P44" s="1"/>
-      <c r="Q44" s="1"/>
-      <c r="R44" s="1"/>
-    </row>
-    <row r="45" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
-      <c r="C45" s="1"/>
-      <c r="D45" s="1"/>
-      <c r="E45" s="1"/>
-      <c r="F45" s="1"/>
-      <c r="G45" s="1"/>
-      <c r="H45" s="1"/>
-      <c r="I45" s="1"/>
-      <c r="J45" s="1"/>
-      <c r="K45" s="1"/>
-      <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
-      <c r="N45" s="1"/>
-      <c r="O45" s="1"/>
-      <c r="P45" s="1"/>
-      <c r="Q45" s="1"/>
-      <c r="R45" s="1"/>
-    </row>
-    <row r="46" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
-      <c r="C46" s="1"/>
-      <c r="D46" s="1"/>
-      <c r="E46" s="1"/>
-      <c r="F46" s="1"/>
-      <c r="G46" s="1"/>
-      <c r="H46" s="1"/>
-      <c r="I46" s="1"/>
-      <c r="J46" s="1"/>
-      <c r="K46" s="1"/>
-      <c r="L46" s="1"/>
-      <c r="M46" s="1"/>
-      <c r="N46" s="1"/>
-      <c r="O46" s="1"/>
-      <c r="P46" s="1"/>
-      <c r="Q46" s="1"/>
-      <c r="R46" s="1"/>
-    </row>
-    <row r="47" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
-      <c r="C47" s="1"/>
-      <c r="D47" s="1"/>
-      <c r="E47" s="1"/>
-      <c r="F47" s="1"/>
-      <c r="G47" s="1"/>
-      <c r="H47" s="1"/>
-      <c r="I47" s="1"/>
-      <c r="J47" s="1"/>
-      <c r="K47" s="1"/>
-      <c r="L47" s="1"/>
-      <c r="M47" s="1"/>
-      <c r="N47" s="1"/>
-      <c r="O47" s="1"/>
-      <c r="P47" s="1"/>
-      <c r="Q47" s="1"/>
-      <c r="R47" s="1"/>
-    </row>
-    <row r="48" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
-      <c r="C48" s="1"/>
-      <c r="D48" s="1"/>
-      <c r="E48" s="1"/>
-      <c r="F48" s="1"/>
-      <c r="G48" s="1"/>
-      <c r="H48" s="1"/>
-      <c r="I48" s="1"/>
-      <c r="J48" s="1"/>
-      <c r="K48" s="1"/>
-      <c r="L48" s="1"/>
-      <c r="M48" s="1"/>
-      <c r="N48" s="1"/>
-      <c r="O48" s="1"/>
-      <c r="P48" s="1"/>
-      <c r="Q48" s="1"/>
-      <c r="R48" s="1"/>
-    </row>
-    <row r="49" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
-      <c r="C49" s="1"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="1"/>
-      <c r="K49" s="1"/>
-      <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
-      <c r="N49" s="1"/>
-      <c r="O49" s="1"/>
-      <c r="P49" s="1"/>
-      <c r="Q49" s="1"/>
-      <c r="R49" s="1"/>
-    </row>
-    <row r="50" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
-      <c r="C50" s="1"/>
-      <c r="D50" s="1"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="1"/>
-      <c r="K50" s="1"/>
-      <c r="L50" s="1"/>
-      <c r="M50" s="1"/>
-      <c r="N50" s="1"/>
-      <c r="O50" s="1"/>
-      <c r="P50" s="1"/>
-      <c r="Q50" s="1"/>
-      <c r="R50" s="1"/>
-    </row>
-    <row r="51" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
-      <c r="D51" s="1"/>
-      <c r="E51" s="1"/>
-      <c r="F51" s="1"/>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
-      <c r="J51" s="1"/>
-      <c r="K51" s="1"/>
-      <c r="L51" s="1"/>
-      <c r="M51" s="1"/>
-      <c r="N51" s="1"/>
-      <c r="O51" s="1"/>
-      <c r="P51" s="1"/>
-      <c r="Q51" s="1"/>
-      <c r="R51" s="1"/>
-    </row>
-    <row r="52" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
-      <c r="C52" s="1"/>
-      <c r="D52" s="1"/>
-      <c r="E52" s="1"/>
-      <c r="F52" s="1"/>
-      <c r="G52" s="1"/>
-      <c r="H52" s="1"/>
-      <c r="I52" s="1"/>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
-      <c r="L52" s="1"/>
-      <c r="M52" s="1"/>
-      <c r="N52" s="1"/>
-      <c r="O52" s="1"/>
-      <c r="P52" s="1"/>
-      <c r="Q52" s="1"/>
-      <c r="R52" s="1"/>
-    </row>
-    <row r="53" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="1"/>
-      <c r="E53" s="1"/>
-      <c r="F53" s="1"/>
-      <c r="G53" s="1"/>
-      <c r="H53" s="1"/>
-      <c r="I53" s="1"/>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
-      <c r="M53" s="1"/>
-      <c r="N53" s="1"/>
-      <c r="O53" s="1"/>
-      <c r="P53" s="1"/>
-      <c r="Q53" s="1"/>
-      <c r="R53" s="1"/>
-    </row>
-    <row r="54" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="1"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="1"/>
-      <c r="G54" s="1"/>
-      <c r="H54" s="1"/>
-      <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
-      <c r="M54" s="1"/>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
-      <c r="R54" s="1"/>
-    </row>
-    <row r="55" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
-      <c r="C55" s="1"/>
-      <c r="D55" s="1"/>
-      <c r="E55" s="1"/>
-      <c r="F55" s="1"/>
-      <c r="G55" s="1"/>
-      <c r="H55" s="1"/>
-      <c r="I55" s="1"/>
-      <c r="J55" s="1"/>
-      <c r="K55" s="1"/>
-      <c r="L55" s="1"/>
-      <c r="M55" s="1"/>
-      <c r="N55" s="1"/>
-      <c r="O55" s="1"/>
-      <c r="P55" s="1"/>
-      <c r="Q55" s="1"/>
-      <c r="R55" s="1"/>
-    </row>
-    <row r="56" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
-      <c r="C56" s="1"/>
-      <c r="D56" s="1"/>
-      <c r="E56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="H56" s="1"/>
-      <c r="I56" s="1"/>
-      <c r="J56" s="1"/>
-      <c r="K56" s="1"/>
-      <c r="L56" s="1"/>
-      <c r="M56" s="1"/>
-      <c r="N56" s="1"/>
-      <c r="O56" s="1"/>
-      <c r="P56" s="1"/>
-      <c r="Q56" s="1"/>
-      <c r="R56" s="1"/>
-    </row>
-    <row r="57" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
-      <c r="C57" s="1"/>
-      <c r="D57" s="1"/>
-      <c r="E57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="H57" s="1"/>
-      <c r="I57" s="1"/>
-      <c r="J57" s="1"/>
-      <c r="K57" s="1"/>
-      <c r="L57" s="1"/>
-      <c r="M57" s="1"/>
-      <c r="N57" s="1"/>
-      <c r="O57" s="1"/>
-      <c r="P57" s="1"/>
-      <c r="Q57" s="1"/>
-      <c r="R57" s="1"/>
-    </row>
-    <row r="58" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
-      <c r="C58" s="1"/>
-      <c r="D58" s="1"/>
-      <c r="E58" s="1"/>
-      <c r="F58" s="1"/>
-      <c r="G58" s="1"/>
-      <c r="H58" s="1"/>
-      <c r="I58" s="1"/>
-      <c r="J58" s="1"/>
-      <c r="K58" s="1"/>
-      <c r="L58" s="1"/>
-      <c r="M58" s="1"/>
-      <c r="N58" s="1"/>
-      <c r="O58" s="1"/>
-      <c r="P58" s="1"/>
-      <c r="Q58" s="1"/>
-      <c r="R58" s="1"/>
-    </row>
-    <row r="59" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
-      <c r="C59" s="1"/>
-      <c r="D59" s="1"/>
-      <c r="E59" s="1"/>
-      <c r="F59" s="1"/>
-      <c r="G59" s="1"/>
-      <c r="H59" s="1"/>
-      <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="1"/>
-      <c r="L59" s="1"/>
-      <c r="M59" s="1"/>
-      <c r="N59" s="1"/>
-      <c r="O59" s="1"/>
-      <c r="P59" s="1"/>
-      <c r="Q59" s="1"/>
-      <c r="R59" s="1"/>
-    </row>
-    <row r="60" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
-      <c r="C60" s="1"/>
-      <c r="D60" s="1"/>
-      <c r="E60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
-      <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
-      <c r="M60" s="1"/>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
-      <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
-      <c r="R60" s="1"/>
-    </row>
-    <row r="61" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
-      <c r="C61" s="1"/>
-      <c r="D61" s="1"/>
-      <c r="E61" s="1"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="H61" s="1"/>
-      <c r="I61" s="1"/>
-      <c r="J61" s="1"/>
-      <c r="K61" s="1"/>
-      <c r="L61" s="1"/>
-      <c r="M61" s="1"/>
-      <c r="N61" s="1"/>
-      <c r="O61" s="1"/>
-      <c r="P61" s="1"/>
-      <c r="Q61" s="1"/>
-      <c r="R61" s="1"/>
-    </row>
-    <row r="62" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
-      <c r="C62" s="1"/>
-      <c r="D62" s="1"/>
-      <c r="E62" s="1"/>
-      <c r="F62" s="1"/>
-      <c r="G62" s="1"/>
-      <c r="H62" s="1"/>
-      <c r="I62" s="1"/>
-      <c r="J62" s="1"/>
-      <c r="K62" s="1"/>
-      <c r="L62" s="1"/>
-      <c r="M62" s="1"/>
-      <c r="N62" s="1"/>
-      <c r="O62" s="1"/>
-      <c r="P62" s="1"/>
-      <c r="Q62" s="1"/>
-      <c r="R62" s="1"/>
-    </row>
-    <row r="63" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
-      <c r="C63" s="1"/>
-      <c r="D63" s="1"/>
-      <c r="E63" s="1"/>
-      <c r="F63" s="1"/>
-      <c r="G63" s="1"/>
-      <c r="H63" s="1"/>
-      <c r="I63" s="1"/>
-      <c r="J63" s="1"/>
-      <c r="K63" s="1"/>
-      <c r="L63" s="1"/>
-      <c r="M63" s="1"/>
-      <c r="N63" s="1"/>
-      <c r="O63" s="1"/>
-      <c r="P63" s="1"/>
-      <c r="Q63" s="1"/>
-      <c r="R63" s="1"/>
-    </row>
-    <row r="64" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
-      <c r="C64" s="1"/>
-      <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
-      <c r="G64" s="1"/>
-      <c r="H64" s="1"/>
-      <c r="I64" s="1"/>
-      <c r="J64" s="1"/>
-      <c r="K64" s="1"/>
-      <c r="L64" s="1"/>
-      <c r="M64" s="1"/>
-      <c r="N64" s="1"/>
-      <c r="O64" s="1"/>
-      <c r="P64" s="1"/>
-      <c r="Q64" s="1"/>
-      <c r="R64" s="1"/>
-    </row>
-    <row r="65" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
-      <c r="C65" s="1"/>
-      <c r="D65" s="1"/>
-      <c r="E65" s="1"/>
-      <c r="F65" s="1"/>
-      <c r="G65" s="1"/>
-      <c r="H65" s="1"/>
-      <c r="I65" s="1"/>
-      <c r="J65" s="1"/>
-      <c r="K65" s="1"/>
-      <c r="L65" s="1"/>
-      <c r="M65" s="1"/>
-      <c r="N65" s="1"/>
-      <c r="O65" s="1"/>
-      <c r="P65" s="1"/>
-      <c r="Q65" s="1"/>
-      <c r="R65" s="1"/>
-    </row>
-    <row r="66" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
-      <c r="C66" s="1"/>
-      <c r="D66" s="1"/>
-      <c r="E66" s="1"/>
-      <c r="F66" s="1"/>
-      <c r="G66" s="1"/>
-      <c r="H66" s="1"/>
-      <c r="I66" s="1"/>
-      <c r="J66" s="1"/>
-      <c r="K66" s="1"/>
-      <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
-      <c r="N66" s="1"/>
-      <c r="O66" s="1"/>
-      <c r="P66" s="1"/>
-      <c r="Q66" s="1"/>
-      <c r="R66" s="1"/>
-    </row>
-    <row r="67" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
-      <c r="C67" s="1"/>
-      <c r="D67" s="1"/>
-      <c r="E67" s="1"/>
-      <c r="F67" s="1"/>
-      <c r="G67" s="1"/>
-      <c r="H67" s="1"/>
-      <c r="I67" s="1"/>
-      <c r="J67" s="1"/>
-      <c r="K67" s="1"/>
-      <c r="L67" s="1"/>
-      <c r="M67" s="1"/>
-      <c r="N67" s="1"/>
-      <c r="O67" s="1"/>
-      <c r="P67" s="1"/>
-      <c r="Q67" s="1"/>
-      <c r="R67" s="1"/>
-    </row>
-    <row r="68" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
-      <c r="C68" s="1"/>
-      <c r="D68" s="1"/>
-      <c r="E68" s="1"/>
-      <c r="F68" s="1"/>
-      <c r="G68" s="1"/>
-      <c r="H68" s="1"/>
-      <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-      <c r="M68" s="1"/>
-      <c r="N68" s="1"/>
-      <c r="O68" s="1"/>
-      <c r="P68" s="1"/>
-      <c r="Q68" s="1"/>
-      <c r="R68" s="1"/>
-    </row>
-    <row r="69" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
-      <c r="C69" s="1"/>
-      <c r="D69" s="1"/>
-      <c r="E69" s="1"/>
-      <c r="F69" s="1"/>
-      <c r="G69" s="1"/>
-      <c r="H69" s="1"/>
-      <c r="I69" s="1"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-      <c r="M69" s="1"/>
-      <c r="N69" s="1"/>
-      <c r="O69" s="1"/>
-      <c r="P69" s="1"/>
-      <c r="Q69" s="1"/>
-      <c r="R69" s="1"/>
-    </row>
-    <row r="70" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
-      <c r="C70" s="1"/>
-      <c r="D70" s="1"/>
-      <c r="E70" s="1"/>
-      <c r="F70" s="1"/>
-      <c r="G70" s="1"/>
-      <c r="H70" s="1"/>
-      <c r="I70" s="1"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-      <c r="M70" s="1"/>
-      <c r="N70" s="1"/>
-      <c r="O70" s="1"/>
-      <c r="P70" s="1"/>
-      <c r="Q70" s="1"/>
-      <c r="R70" s="1"/>
-    </row>
-    <row r="71" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
-      <c r="C71" s="1"/>
-      <c r="D71" s="1"/>
-      <c r="E71" s="1"/>
-      <c r="F71" s="1"/>
-      <c r="G71" s="1"/>
-      <c r="H71" s="1"/>
-      <c r="I71" s="1"/>
-      <c r="J71" s="1"/>
-      <c r="K71" s="1"/>
-      <c r="L71" s="1"/>
-      <c r="M71" s="1"/>
-      <c r="N71" s="1"/>
-      <c r="O71" s="1"/>
-      <c r="P71" s="1"/>
-      <c r="Q71" s="1"/>
-      <c r="R71" s="1"/>
-    </row>
-    <row r="72" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
-      <c r="H72" s="1"/>
-      <c r="I72" s="1"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-      <c r="M72" s="1"/>
-      <c r="N72" s="1"/>
-      <c r="O72" s="1"/>
-      <c r="P72" s="1"/>
-      <c r="Q72" s="1"/>
-      <c r="R72" s="1"/>
-    </row>
-    <row r="73" ht="15.75" customHeight="1" spans="1:18" x14ac:dyDescent="0.25">
-      <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
-      <c r="C73" s="1"/>
-      <c r="D73" s="1"/>
-      <c r="E73" s="1"/>
-      <c r="F73" s="1"/>
-      <c r="G73" s="1"/>
-      <c r="H73" s="1"/>
-      <c r="I73" s="1"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
-      <c r="N73" s="1"/>
-      <c r="O73" s="1"/>
-      <c r="P73" s="1"/>
-      <c r="Q73" s="1"/>
-      <c r="R73" s="1"/>
-    </row>
+    </row>
+    <row r="13" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="14" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="15" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="18" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <conditionalFormatting sqref="A1:BB1">
-    <cfRule type="expression" dxfId="21" priority="1">
+    <cfRule type="expression" dxfId="22" priority="1">
       <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BB$1,A1)&gt;1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="22" priority="2">
+    <cfRule type="expression" dxfId="23" priority="2">
       <formula>AND(OR(A1="audio",LEFT(A1,7)="audio::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="video",LEFT(A1,7)="video::"),COUNTA(A$2:A$1073)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="23" priority="3">
+    <cfRule type="expression" dxfId="24" priority="3">
       <formula>AND(A1&lt;&gt;"",COUNTA(A$2:A$1073)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="24" priority="4">
+    <cfRule type="expression" dxfId="25" priority="4">
       <formula>OR(A1="audio",LEFT(A1,7)="audio::",A1="image",LEFT(A1,7)="image::",A1="label",LEFT(A1,7)="label::",A1="video",LEFT(A1,7)="video::")</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="25" priority="5">
+    <cfRule type="expression" dxfId="26" priority="5">
       <formula>A1&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="A2:BB1073">
-    <cfRule type="expression" dxfId="26" priority="1">
+    <cfRule type="expression" dxfId="27" priority="1">
       <formula>AND(A2&lt;&gt;"",A$1="")</formula>
     </cfRule>
   </conditionalFormatting>
@@ -5830,46 +3853,46 @@
       <formula1>'chtx'!$C$2:$C$7</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.752083333333333" bottom="0.752083333333333" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" copies="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z2"/>
-  <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.44140625" customHeight="1"/>
+  <dimension ref="A1:V2"/>
+  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.4453125" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="21" style="1" customWidth="1"/>
-    <col min="2" max="2" width="28.5546875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="24.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="14.44140625" style="2" customWidth="1"/>
-    <col min="5" max="16384" width="14.44140625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="24.56" style="1" customWidth="1"/>
+    <col min="3" max="3" width="14.44" style="2" customWidth="1"/>
+    <col min="4" max="4" width="32.6" style="1" customWidth="1"/>
+    <col min="5" max="54" width="14.44" style="1" customWidth="1"/>
+    <col min="55" max="55" width="9" style="1" customWidth="1"/>
+    <col min="56" max="56" width="9" style="1" customWidth="1"/>
+    <col min="57" max="57" width="9" style="1" customWidth="1"/>
+    <col min="58" max="58" width="9" style="1" customWidth="1"/>
+    <col min="59" max="16380" width="14.44" style="1" customWidth="1"/>
+    <col min="16381" max="16384" width="11.53" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15.75" customHeight="1" spans="1:26" s="3" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" ht="15.75" customHeight="1" spans="1:22" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>195</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>196</v>
-      </c>
+        <v>181</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>183</v>
+      </c>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
       <c r="J1" s="1"/>
@@ -5885,68 +3908,57 @@
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
       <c r="V1" s="1"/>
-      <c r="W1" s="1"/>
-      <c r="X1" s="1"/>
-      <c r="Y1" s="1"/>
-      <c r="Z1" s="1"/>
-    </row>
-    <row r="2" ht="15.75" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" ht="15.75" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>197</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>198</v>
-      </c>
-      <c r="C2" s="1" t="str">
+        <v>184</v>
+      </c>
+      <c r="B2" s="1" t="str">
         <f>TEXT(NOW(), "yyyy-mm-dd_HH-MM")</f>
-        <v>20260722230251</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1" t="s">
-        <v>201</v>
+        <v>20260724164712</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>186</v>
       </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="A1:BF1">
-    <cfRule type="expression" dxfId="27" priority="1">
-      <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BF$1,A1)&gt;1)</formula>
+  <conditionalFormatting sqref="A1:BC1">
+    <cfRule type="expression" dxfId="28" priority="1">
+      <formula>AND(A1&lt;&gt;"",COUNTIF($A$1:$BC$1,A1)&gt;1)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="28" priority="2">
+    <cfRule type="expression" dxfId="29" priority="2">
       <formula>AND(A1&lt;&gt;"",NOT(NOT(ISERROR(MATCH(A1,{"allow_choice_duplicates","form_title","namespaces","style","version"},0)))))</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="29" priority="3">
+    <cfRule type="expression" dxfId="30" priority="3">
       <formula>AND(A1&lt;&gt;"",COUNTA(A$2:A$1002)=0)</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="30" priority="4">
+    <cfRule type="expression" dxfId="31" priority="4">
       <formula>NOT(ISERROR(MATCH(A1,{"allow_choice_duplicates","form_title","namespaces","style","version"},0)))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D2:D1002">
-    <cfRule type="expression" dxfId="31" priority="1">
-      <formula>AND(D2&lt;&gt;"",D2&lt;&gt;"pages")</formula>
+  <conditionalFormatting sqref="C2:C1002">
+    <cfRule type="expression" dxfId="32" priority="1">
+      <formula>AND(C2&lt;&gt;"",C2&lt;&gt;"pages")</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="A2:BF1002">
-    <cfRule type="expression" dxfId="32" priority="1">
+  <conditionalFormatting sqref="A2:BC1002">
+    <cfRule type="expression" dxfId="33" priority="1">
       <formula>AND(A2&lt;&gt;"",A$1="")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Column warning" error="Unexpected column name." sqref="A1:BF1">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="information" errorTitle="Column warning" error="Unexpected column name." sqref="A1:BC1">
       <formula1>'chtx'!$E$2:$E$6</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="This column only accepts &quot;pages&quot; or an empty value." sqref="D2:D1002">
+    <dataValidation type="list" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="Invalid value" error="This column only accepts &quot;pages&quot; or an empty value." sqref="C2:C1002">
       <formula1>",pages"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.752083333333333" bottom="0.752083333333333" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" copies="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -5954,15 +3966,15 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:W1000"/>
-  <sheetFormatPr defaultRowHeight="13.2" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.44140625" customHeight="1"/>
+  <sheetFormatPr defaultRowHeight="12.75" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0" defaultColWidth="14.4453125" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="28.33203125" customWidth="1"/>
-    <col min="2" max="23" width="45.88671875" customWidth="1"/>
+    <col min="1" max="1" width="28.33" customWidth="1"/>
+    <col min="2" max="23" width="45.88" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>1</v>
@@ -5971,22 +3983,22 @@
         <v>2</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H1" s="10" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="I1" s="11" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="J1" s="12"/>
       <c r="K1" s="12"/>
@@ -6005,13 +4017,13 @@
     </row>
     <row r="2" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B2" s="13" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="C2" s="13" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D2" s="13"/>
       <c r="E2" s="13"/>
@@ -6036,13 +4048,13 @@
     </row>
     <row r="3" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="13" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="B3" s="13" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C3" s="13" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D3" s="13"/>
       <c r="E3" s="13"/>
@@ -6092,13 +4104,13 @@
     </row>
     <row r="5" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B5" s="13" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C5" s="13" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="D5" s="13"/>
       <c r="E5" s="13"/>
@@ -6123,13 +4135,13 @@
     </row>
     <row r="6" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B6" s="13" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="C6" s="13" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D6" s="13"/>
       <c r="E6" s="13"/>
@@ -6154,13 +4166,13 @@
     </row>
     <row r="7" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="C7" s="13" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="D7" s="13"/>
       <c r="E7" s="13"/>
@@ -6185,13 +4197,13 @@
     </row>
     <row r="8" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B8" s="13" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="C8" s="13" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="D8" s="13"/>
       <c r="E8" s="13"/>
@@ -6216,13 +4228,13 @@
     </row>
     <row r="9" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="C9" s="13" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="D9" s="13"/>
       <c r="E9" s="13"/>
@@ -6272,13 +4284,13 @@
     </row>
     <row r="11" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C11" s="13" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
@@ -6303,13 +4315,13 @@
     </row>
     <row r="12" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B12" s="13" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
@@ -6334,13 +4346,13 @@
     </row>
     <row r="13" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B13" s="13" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C13" s="13" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
@@ -6365,13 +4377,13 @@
     </row>
     <row r="14" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B14" s="13" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
@@ -6396,13 +4408,13 @@
     </row>
     <row r="15" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="D15" s="13"/>
       <c r="E15" s="13"/>
@@ -6427,13 +4439,13 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D16" s="13"/>
       <c r="E16" s="13"/>
@@ -6483,13 +4495,13 @@
     </row>
     <row r="18" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="13" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B18" s="13" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="D18" s="13"/>
       <c r="E18" s="13"/>
@@ -6514,13 +4526,13 @@
     </row>
     <row r="19" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="13" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="D19" s="13"/>
       <c r="E19" s="13"/>
@@ -6545,13 +4557,13 @@
     </row>
     <row r="20" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="13" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B20" s="13" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="D20" s="13"/>
       <c r="E20" s="13"/>
@@ -6576,13 +4588,13 @@
     </row>
     <row r="21" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B21" s="13" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="C21" s="13" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="D21" s="13"/>
       <c r="E21" s="13"/>
@@ -6607,13 +4619,13 @@
     </row>
     <row r="22" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="13" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B22" s="13" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="C22" s="13" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="D22" s="13"/>
       <c r="E22" s="13"/>
@@ -6638,13 +4650,13 @@
     </row>
     <row r="23" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="C23" s="13" t="s">
-        <v>239</v>
+        <v>224</v>
       </c>
       <c r="D23" s="13"/>
       <c r="E23" s="13"/>
@@ -6694,13 +4706,13 @@
     </row>
     <row r="25" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="13" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B25" s="13" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="D25" s="13"/>
       <c r="E25" s="13"/>
@@ -6725,13 +4737,13 @@
     </row>
     <row r="26" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="13" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="C26" s="13" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
@@ -6756,13 +4768,13 @@
     </row>
     <row r="27" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="13" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B27" s="13" t="s">
-        <v>245</v>
+        <v>230</v>
       </c>
       <c r="C27" s="13" t="s">
-        <v>246</v>
+        <v>231</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
@@ -6787,13 +4799,13 @@
     </row>
     <row r="28" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="13" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B28" s="13" t="s">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="C28" s="13" t="s">
-        <v>248</v>
+        <v>233</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
@@ -6818,13 +4830,13 @@
     </row>
     <row r="29" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="13" t="s">
-        <v>240</v>
+        <v>225</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C29" s="13" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
@@ -6874,13 +4886,13 @@
     </row>
     <row r="31" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B31" s="13" t="s">
-        <v>250</v>
+        <v>235</v>
       </c>
       <c r="C31" s="13" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
@@ -6905,13 +4917,13 @@
     </row>
     <row r="32" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="13" t="s">
-        <v>249</v>
+        <v>234</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>251</v>
+        <v>236</v>
       </c>
       <c r="C32" s="13" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
@@ -6961,166 +4973,166 @@
     </row>
     <row r="34" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B34" t="str">
-        <f t="shared" ref="B34:B47" si="0">SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C34, "(", ""), ")", "")), " ", "_")</f>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C34, "(", ""), ")", "")), " ", "_")</f>
         <v>combined_oral_contraceptives</v>
       </c>
       <c r="C34" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B35" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C35, "(", ""), ")", "")), " ", "_")</f>
         <v>progesterone_only_pills</v>
       </c>
       <c r="C35" t="s">
-        <v>254</v>
+        <v>239</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B36" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C36, "(", ""), ")", "")), " ", "_")</f>
         <v>injectibles</v>
       </c>
       <c r="C36" t="s">
-        <v>255</v>
+        <v>240</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B37" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C37, "(", ""), ")", "")), " ", "_")</f>
         <v>implants_1_rod</v>
       </c>
       <c r="C37" t="s">
-        <v>256</v>
+        <v>241</v>
       </c>
     </row>
     <row r="38" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B38" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C38, "(", ""), ")", "")), " ", "_")</f>
         <v>implants_2_rods</v>
       </c>
       <c r="C38" t="s">
-        <v>257</v>
+        <v>242</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B39" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C39, "(", ""), ")", "")), " ", "_")</f>
         <v>iud</v>
       </c>
       <c r="C39" t="s">
-        <v>258</v>
+        <v>243</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B40" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C40, "(", ""), ")", "")), " ", "_")</f>
         <v>condoms</v>
       </c>
       <c r="C40" t="s">
-        <v>259</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B41" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C41, "(", ""), ")", "")), " ", "_")</f>
         <v>tubal_ligation</v>
       </c>
       <c r="C41" t="s">
-        <v>260</v>
+        <v>245</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B42" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C42, "(", ""), ")", "")), " ", "_")</f>
         <v>cycle_beads</v>
       </c>
       <c r="C42" t="s">
-        <v>261</v>
+        <v>246</v>
       </c>
     </row>
     <row r="43" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="B43" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C43" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" ht="15.75" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B44">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C44, "(", ""), ")", "")), " ", "_")</f>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B45" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C45, "(", ""), ")", "")), " ", "_")</f>
         <v>wants_to_get_pregnant</v>
       </c>
       <c r="C45" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>262</v>
+        <v>247</v>
       </c>
       <c r="B46" t="str">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C46, "(", ""), ")", "")), " ", "_")</f>
         <v>did_not_want_fp</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" ht="15.75" customHeight="1" spans="2:2" x14ac:dyDescent="0.25">
       <c r="B47">
-        <f t="shared" si="0"/>
+        <f>SUBSTITUTE(LOWER(SUBSTITUTE(SUBSTITUTE(C47, "(", ""), ")", "")), " ", "_")</f>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="14" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="B48" s="14" t="s">
-        <v>266</v>
+        <v>251</v>
       </c>
       <c r="C48" s="14" t="s">
-        <v>267</v>
+        <v>252</v>
       </c>
       <c r="D48" s="14"/>
       <c r="E48" s="14"/>
@@ -7145,13 +5157,13 @@
     </row>
     <row r="49" ht="15.75" customHeight="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>265</v>
+        <v>250</v>
       </c>
       <c r="B49" s="14" t="s">
-        <v>268</v>
+        <v>253</v>
       </c>
       <c r="C49" s="14" t="s">
-        <v>269</v>
+        <v>254</v>
       </c>
       <c r="D49" s="14"/>
       <c r="E49" s="14"/>
@@ -7177,226 +5189,226 @@
     <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="51" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B51" t="s">
-        <v>271</v>
+        <v>256</v>
       </c>
       <c r="C51" t="s">
-        <v>272</v>
+        <v>257</v>
       </c>
     </row>
     <row r="52" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B52" t="s">
-        <v>273</v>
+        <v>258</v>
       </c>
       <c r="C52" t="s">
-        <v>274</v>
+        <v>259</v>
       </c>
     </row>
     <row r="53" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B53" t="s">
-        <v>275</v>
+        <v>260</v>
       </c>
       <c r="C53" t="s">
-        <v>276</v>
+        <v>261</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B54" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="C54" t="s">
-        <v>278</v>
+        <v>263</v>
       </c>
     </row>
     <row r="55" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B55" t="s">
-        <v>279</v>
+        <v>264</v>
       </c>
       <c r="C55" t="s">
-        <v>280</v>
+        <v>265</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>270</v>
+        <v>255</v>
       </c>
       <c r="B56" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C56" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="58" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B58" s="14" t="s">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="C58" s="14" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" s="14" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B59" s="14" t="s">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="C59" s="14" t="s">
-        <v>285</v>
+        <v>270</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" s="14" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B60" s="14" t="s">
-        <v>286</v>
+        <v>271</v>
       </c>
       <c r="C60" s="14" t="s">
-        <v>287</v>
+        <v>272</v>
       </c>
     </row>
     <row r="61" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>281</v>
+        <v>266</v>
       </c>
       <c r="B61" s="14" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C61" s="14" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="63" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" s="12" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B63" s="12" t="s">
-        <v>289</v>
+        <v>274</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>290</v>
+        <v>275</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" s="12" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B64" s="12" t="s">
-        <v>291</v>
+        <v>276</v>
       </c>
       <c r="C64" s="14" t="s">
-        <v>292</v>
+        <v>277</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" s="12" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B65" s="12" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>294</v>
+        <v>279</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" s="12" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B66" s="12" t="s">
-        <v>295</v>
+        <v>280</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>296</v>
+        <v>281</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" s="12" t="s">
-        <v>288</v>
+        <v>273</v>
       </c>
       <c r="B67" s="12" t="s">
-        <v>297</v>
+        <v>282</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>298</v>
+        <v>283</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B69" t="s">
-        <v>300</v>
+        <v>285</v>
       </c>
       <c r="C69" t="s">
-        <v>301</v>
+        <v>286</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>299</v>
+        <v>284</v>
       </c>
       <c r="B70" t="s">
-        <v>302</v>
+        <v>287</v>
       </c>
       <c r="C70" t="s">
-        <v>303</v>
+        <v>288</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B72" t="s">
-        <v>305</v>
+        <v>290</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>263</v>
+        <v>248</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B73" t="s">
-        <v>306</v>
+        <v>291</v>
       </c>
       <c r="C73" t="s">
-        <v>307</v>
+        <v>292</v>
       </c>
     </row>
     <row r="74" ht="15.75" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>304</v>
+        <v>289</v>
       </c>
       <c r="B74" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C74" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
     </row>
     <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8326,8 +6338,8 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <pageMargins left="0.700694444444444" right="0.700694444444444" top="0.752083333333333" bottom="0.752083333333333" header="0.511805555555555" footer="0.511805555555555"/>
-  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="0" copies="1"/>
+  <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" orientation="portrait" horizontalDpi="300" verticalDpi="300" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
@@ -8338,13 +6350,13 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>308</v>
+        <v>293</v>
       </c>
       <c r="C1" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="E1" t="s">
-        <v>310</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
@@ -8352,21 +6364,21 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="E2" t="s">
-        <v>312</v>
+        <v>297</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>311</v>
+        <v>296</v>
       </c>
       <c r="C3" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
       <c r="E3" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
@@ -8374,21 +6386,21 @@
         <v>8</v>
       </c>
       <c r="C4" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
       <c r="E4" t="s">
-        <v>315</v>
+        <v>183</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>316</v>
+        <v>300</v>
       </c>
       <c r="C5" t="s">
-        <v>168</v>
+        <v>158</v>
       </c>
       <c r="E5" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -8399,15 +6411,15 @@
         <v>1</v>
       </c>
       <c r="E6" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="C7" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -8417,22 +6429,22 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>319</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>313</v>
+        <v>298</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>320</v>
+        <v>304</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>321</v>
+        <v>14</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
@@ -8447,17 +6459,17 @@
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>322</v>
+        <v>305</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>323</v>
+        <v>306</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>314</v>
+        <v>299</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
@@ -8467,12 +6479,12 @@
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>324</v>
+        <v>307</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
@@ -8487,7 +6499,7 @@
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
@@ -8497,12 +6509,12 @@
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>326</v>
+        <v>309</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>327</v>
+        <v>310</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
@@ -8512,7 +6524,7 @@
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>318</v>
+        <v>302</v>
       </c>
     </row>
   </sheetData>
